--- a/stories/arbres/TREE-SEC-001.xlsx
+++ b/stories/arbres/TREE-SEC-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sami marche avec Papa, sur le chemin de l'école. Les chaussures font toc toc. Sami arrive au bord. Il s'arrête. Ses pieds restent sur le trottoir. Ses pieds sont au bord. Sa main tient la main de Papa. Papa est l'adulte. Maman les attend près de l'école.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami prend le sac jaune. Ils arrivent près de la boulangerie. Ça sent le pain chaud. Sami s'arrête. Ses pieds restent sur le trottoir, au bord. Sa main tient la main de Papa. Papa dit : je suis là. On attend l'adulte.</t>
+          <t>Sami prend le sac jaune. Ils arrivent près de la boulangerie. Ça sent le pain chaud. Sami s'arrête. Ses pieds restent sur le trottoir, au bord. Sa main tient la main de Papa. Je suis là. On attend l'adulte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1657,6 +1684,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend le sac jaune. Ils arrivent près de la boulangerie. Ça sent le pain chaud. Sami s'arrête. Ses pieds restent sur le trottoir, au bord. Sa main tient la main de Papa.
+papa|Je suis là. On attend l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1874,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -2013,6 +2051,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2199,6 +2242,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon jaune, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2365,6 +2413,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon jaune. Un oiseau chante. Sami tient le ballon jaune contre son manteau. Il s'arrête encore. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2551,6 +2604,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2717,6 +2775,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. Le vent est doux. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2942,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3113,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. Les chaussures font toc toc. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3280,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3451,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. Une feuille tombe. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3618,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3789,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau bleu. Ça sent le pain. Sami pose le seau bleu près de Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3887,6 +3980,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4053,6 +4151,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. Les chaussures font toc toc. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4215,6 +4318,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4381,6 +4489,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. Une feuille tombe. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4543,6 +4656,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4709,6 +4827,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. La cloche sonne loin. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4871,6 +4994,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5037,6 +5165,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. Le vent est doux. Sami garde le doudou dans une main. L'autre main tient Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5223,6 +5356,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5389,6 +5527,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. Une feuille tombe. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5551,6 +5694,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5717,6 +5865,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. La cloche sonne loin. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5879,6 +6032,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6045,6 +6203,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. Un oiseau chante. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6207,6 +6370,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6373,6 +6541,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami met le gilet bleu. Ils arrivent près du petit parc. Un oiseau chante. Sami s'arrête. Ses pieds restent sur le trottoir, au bord. Sa main tient la main de Papa. Papa sourit. On attend l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6557,6 +6730,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -6729,6 +6907,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6915,6 +7098,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon jaune, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7081,6 +7269,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon jaune. Les chaussures font toc toc. Sami tient le ballon jaune contre son manteau. Il s'arrête encore. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7267,6 +7460,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7433,6 +7631,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. Les chaussures font toc toc. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7595,6 +7798,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7761,6 +7969,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. Une feuille tombe. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7923,6 +8136,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8089,6 +8307,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. La cloche sonne loin. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8251,6 +8474,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8417,6 +8645,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau bleu. Une feuille tombe. Sami pose le seau bleu près de Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8603,6 +8836,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8769,6 +9007,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. Une feuille tombe. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8931,6 +9174,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9097,6 +9345,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. La cloche sonne loin. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9259,6 +9512,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9425,6 +9683,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. Un oiseau chante. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9587,6 +9850,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9753,6 +10021,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. La cloche sonne loin. Sami garde le doudou dans une main. L'autre main tient Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9939,6 +10212,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10105,6 +10383,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. La cloche sonne loin. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10267,6 +10550,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10433,6 +10721,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. Un oiseau chante. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10595,6 +10888,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10761,6 +11059,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. Ça sent le pain. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10923,6 +11226,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11089,6 +11397,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami met le bonnet blanc. Ils arrivent au portail de l'école. La cloche sonne, loin. Sami s'arrête. Ses pieds restent sur le trottoir, au bord. Sa main tient la main de Papa. Maman fait un petit signe.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11273,6 +11586,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -11445,6 +11763,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11631,6 +11954,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon jaune, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11797,6 +12125,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon jaune. Un oiseau chante. Sami tient le ballon jaune contre son manteau. Il s'arrête encore. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11983,6 +12316,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12149,6 +12487,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. Une feuille tombe. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12311,6 +12654,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12477,6 +12825,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. La cloche sonne loin. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12639,6 +12992,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12805,6 +13163,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. Un oiseau chante. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12967,6 +13330,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13133,6 +13501,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau bleu. Ça sent le pain. Sami pose le seau bleu près de Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13319,6 +13692,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13485,6 +13863,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. La cloche sonne loin. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13647,6 +14030,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13813,6 +14201,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. Un oiseau chante. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13975,6 +14368,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14141,6 +14539,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. Ça sent le pain. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14303,6 +14706,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14469,6 +14877,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. Le vent est doux. Sami garde le doudou dans une main. L'autre main tient Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14655,6 +15068,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14821,6 +15239,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chat. Un oiseau chante. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14983,6 +15406,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15149,6 +15577,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit le chien. Ça sent le pain. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15311,6 +15744,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15477,6 +15915,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit la poule. Le vent est doux. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15639,6 +16082,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15657,7 +16105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15674,6 +16122,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-001.xlsx
+++ b/stories/arbres/TREE-SEC-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sami marche avec Papa, sur le chemin de l'école. Les chaussures font toc toc. Sami arrive au bord. Il s'arrête. Ses pieds restent sur le trottoir. Ses pieds sont au bord. Sa main tient la main de Papa. Papa est l'adulte. Maman les attend près de l'école.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1690,6 +1697,7 @@
 papa|Je suis là. On attend l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1881,6 +1889,7 @@
           <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2056,6 +2065,7 @@
           <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2247,6 +2257,7 @@
           <t>narrateur|On peut prendre le ballon jaune, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2418,6 +2429,7 @@
           <t>narrateur|Sami a choisi le ballon jaune. Un oiseau chante. Sami tient le ballon jaune contre son manteau. Il s'arrête encore. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2607,6 +2619,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2780,6 +2797,7 @@
           <t>narrateur|Sami voit le chat. Le vent est doux. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2947,6 +2965,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3118,6 +3137,11 @@
           <t>narrateur|Sami voit le chien. Les chaussures font toc toc. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3285,6 +3309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3456,6 +3481,7 @@
           <t>narrateur|Sami voit la poule. Une feuille tombe. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3623,6 +3649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3794,6 +3821,7 @@
           <t>narrateur|Sami a choisi le seau bleu. Ça sent le pain. Sami pose le seau bleu près de Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3983,6 +4011,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4156,6 +4189,7 @@
           <t>narrateur|Sami voit le chat. Les chaussures font toc toc. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4323,6 +4357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4494,6 +4529,11 @@
           <t>narrateur|Sami voit le chien. Une feuille tombe. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4661,6 +4701,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4832,6 +4873,7 @@
           <t>narrateur|Sami voit la poule. La cloche sonne loin. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4999,6 +5041,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5170,6 +5213,7 @@
           <t>narrateur|Sami a choisi le doudou. Le vent est doux. Sami garde le doudou dans une main. L'autre main tient Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5359,6 +5403,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5532,6 +5581,7 @@
           <t>narrateur|Sami voit le chat. Une feuille tombe. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5699,6 +5749,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5870,6 +5921,11 @@
           <t>narrateur|Sami voit le chien. La cloche sonne loin. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6037,6 +6093,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6208,6 +6265,7 @@
           <t>narrateur|Sami voit la poule. Un oiseau chante. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6375,6 +6433,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6546,6 +6605,11 @@
           <t>narrateur|Sami met le gilet bleu. Ils arrivent près du petit parc. Un oiseau chante. Sami s'arrête. Ses pieds restent sur le trottoir, au bord. Sa main tient la main de Papa. Papa sourit. On attend l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6737,6 +6801,7 @@
           <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6912,6 +6977,7 @@
           <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7103,6 +7169,7 @@
           <t>narrateur|On peut prendre le ballon jaune, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7274,6 +7341,7 @@
           <t>narrateur|Sami a choisi le ballon jaune. Les chaussures font toc toc. Sami tient le ballon jaune contre son manteau. Il s'arrête encore. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7463,6 +7531,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7636,6 +7709,7 @@
           <t>narrateur|Sami voit le chat. Les chaussures font toc toc. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7803,6 +7877,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7974,6 +8049,11 @@
           <t>narrateur|Sami voit le chien. Une feuille tombe. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8141,6 +8221,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8312,6 +8393,7 @@
           <t>narrateur|Sami voit la poule. La cloche sonne loin. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8479,6 +8561,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8650,6 +8733,7 @@
           <t>narrateur|Sami a choisi le seau bleu. Une feuille tombe. Sami pose le seau bleu près de Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8839,6 +8923,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -9012,6 +9101,7 @@
           <t>narrateur|Sami voit le chat. Une feuille tombe. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9179,6 +9269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9350,6 +9441,11 @@
           <t>narrateur|Sami voit le chien. La cloche sonne loin. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9517,6 +9613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9688,6 +9785,7 @@
           <t>narrateur|Sami voit la poule. Un oiseau chante. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9855,6 +9953,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10026,6 +10125,7 @@
           <t>narrateur|Sami a choisi le doudou. La cloche sonne loin. Sami garde le doudou dans une main. L'autre main tient Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10215,6 +10315,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10388,6 +10493,7 @@
           <t>narrateur|Sami voit le chat. La cloche sonne loin. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10555,6 +10661,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10726,6 +10833,11 @@
           <t>narrateur|Sami voit le chien. Un oiseau chante. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10893,6 +11005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11064,6 +11177,7 @@
           <t>narrateur|Sami voit la poule. Ça sent le pain. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11231,6 +11345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11402,6 +11517,7 @@
           <t>narrateur|Sami met le bonnet blanc. Ils arrivent au portail de l'école. La cloche sonne, loin. Sami s'arrête. Ses pieds restent sur le trottoir, au bord. Sa main tient la main de Papa. Maman fait un petit signe.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11593,6 +11709,7 @@
           <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11768,6 +11885,7 @@
           <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11959,6 +12077,7 @@
           <t>narrateur|On peut prendre le ballon jaune, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12130,6 +12249,7 @@
           <t>narrateur|Sami a choisi le ballon jaune. Un oiseau chante. Sami tient le ballon jaune contre son manteau. Il s'arrête encore. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12319,6 +12439,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12492,6 +12617,7 @@
           <t>narrateur|Sami voit le chat. Une feuille tombe. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12659,6 +12785,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12830,6 +12957,11 @@
           <t>narrateur|Sami voit le chien. La cloche sonne loin. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12997,6 +13129,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13168,6 +13301,7 @@
           <t>narrateur|Sami voit la poule. Un oiseau chante. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13335,6 +13469,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13506,6 +13641,7 @@
           <t>narrateur|Sami a choisi le seau bleu. Ça sent le pain. Sami pose le seau bleu près de Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13695,6 +13831,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13868,6 +14009,7 @@
           <t>narrateur|Sami voit le chat. La cloche sonne loin. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14035,6 +14177,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14206,6 +14349,11 @@
           <t>narrateur|Sami voit le chien. Un oiseau chante. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14373,6 +14521,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14544,6 +14693,7 @@
           <t>narrateur|Sami voit la poule. Ça sent le pain. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14711,6 +14861,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14882,6 +15033,7 @@
           <t>narrateur|Sami a choisi le doudou. Le vent est doux. Sami garde le doudou dans une main. L'autre main tient Papa. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15071,6 +15223,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15244,6 +15401,7 @@
           <t>narrateur|Sami voit le chat. Un oiseau chante. Le chat miaule derrière une grille. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15411,6 +15569,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15582,6 +15741,11 @@
           <t>narrateur|Sami voit le chien. Ça sent le pain. Le chien attend sur un paillasson. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15749,6 +15913,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15920,6 +16085,7 @@
           <t>narrateur|Sami voit la poule. Le vent est doux. La poule picore dans un jardin. Sami reste arrêté. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Sami dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16087,6 +16253,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16105,7 +16272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16129,6 +16296,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16143,7 +16324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16330,6 +16511,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
